--- a/UNITS-BIBLE.xlsx
+++ b/UNITS-BIBLE.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +31,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -60,11 +60,6 @@
       <color rgb="009C6500"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -75,22 +70,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F4F6F"/>
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B7DFB7"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B6B6"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,19 +115,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -146,22 +138,16 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,9 +516,9 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -997,16 +983,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1070,12 +1056,12 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1105,12 +1091,12 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1140,12 +1126,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1175,12 +1161,12 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1210,12 +1196,12 @@
           <t>Dispatch / 4</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1245,12 +1231,12 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1280,12 +1266,12 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1315,12 +1301,12 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1350,12 +1336,12 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1385,12 +1371,12 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1420,12 +1406,12 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1455,12 +1441,12 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1490,12 +1476,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1525,12 +1511,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1560,12 +1546,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1595,12 +1581,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1630,12 +1616,12 @@
           <t>Dispatch</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1665,12 +1651,12 @@
           <t>2 PK-CASCADE</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1700,12 +1686,12 @@
           <t>2 PK-CASCADE</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1735,14 +1721,14 @@
           <t>defect</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1743,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>rejected-materials.ts:154</t>
+          <t>rejected-materials.html:63</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>qty_rejected / weight</t>
+          <t>qty_rejected_units, type-gated. WAS ALREADY OK — the survey named the wrong line</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1770,14 +1756,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>— (survey error)</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1783,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>received_qty / weight</t>
+          <t>received_units</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1805,14 +1791,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>S109 proven</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1818,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>received_qty / weight</t>
+          <t>received_units. DEPLOYED, NOT SCREEN-PROVEN</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1840,14 +1826,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>S109 unproven</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1853,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>received_qty / weight</t>
+          <t>received_units</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1875,14 +1861,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>S109 proven</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1888,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>getWdu on received_qty</t>
+          <t>getWdu on received_qty. NOT a repoint — the helper divides</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1910,14 +1896,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>row 46 sitting</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1918,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>product-traceability.ts:109</t>
+          <t>product-traceability.ts:113</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>received_qty / weight</t>
+          <t>received_units. WAS ALREADY OK — carries its own comment</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1945,14 +1931,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>— (survey error)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1958,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>inventory / weight</t>
+          <t>inventory_units, x weight at :885. WAS ALREADY OK</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1980,14 +1966,14 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>— (survey error)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2007,7 +1993,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>(inventory/batch) x (batch/weight)</t>
+          <t>inventory_units. Kg half left reading inventory by design</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2015,14 +2001,14 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>S109 proven</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2028,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>qty_rejected / weight</t>
+          <t>rmp.qty_rejected_units, CTE type-gated to Product. BOTH BOXES</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -2050,14 +2036,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>S109 proven</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2058,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>add-dispatch-v2.ts:194</t>
+          <t>add-dispatch-v2.ts:183,194</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>divides, rounds, STORES packing_units</t>
+          <t>sums the operator's TYPED qtyWdu. No division</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2085,14 +2071,14 @@
           <t>2 PK-CASCADE</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>S109 proven</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -2120,14 +2106,14 @@
           <t>4 PRD-TO-DATE</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Step 4a</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Step 3a</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2155,14 +2141,14 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Step 4b</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Step 3b</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2190,14 +2176,14 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Step 4c</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Step 3c</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2225,14 +2211,14 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Step 4d</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Step 3d</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2260,14 +2246,14 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2295,14 +2281,14 @@
           <t>1 ING-REQ</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2327,17 +2313,17 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>1 ING-REQ</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2343,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>subtracts Kg terms, then divides</t>
+          <t>five Kg terms, then divides</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2365,14 +2351,14 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2368,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>IP trace — backward</t>
+          <t>IP trace backward</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2392,22 +2378,22 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>qty_allocated / weight</t>
+          <t>qty_allocated / weight, no whd_flag filter</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1 ING-REQ</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2403,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IP trace — forward</t>
+          <t>IP trace forward</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2432,17 +2418,17 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1 ING-REQ</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2462,22 +2448,22 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>serves Kg only, no unit figure</t>
+          <t>no unit column exists yet</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1 ING-REQ</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Step 6</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2497,22 +2483,22 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>serves Kg only, no unit figure</t>
+          <t>no unit column exists yet</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1 ING-REQ</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Step 7</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2508,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Product return — stock balance</t>
+          <t>Product return stock balance</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2532,7 +2518,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>adds back to Kg only</t>
+          <t>adds Kg back, never touches inventory_units</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2540,14 +2526,14 @@
           <t>3 STOCK ON HAND</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Step 7</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2572,15 +2558,15 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>MISLABEL</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -2602,20 +2588,20 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>qty / weight — materials are Kg by design</t>
+          <t>Kg-anchored, may be correct by design</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -2637,20 +2623,20 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>callers pass DIFFERENT sources</t>
+          <t>some callers pass Kg and are CORRECT</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Own sitting</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
+          <t>4 PRD-TO-DATE</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>own sitting</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -2677,17 +2663,52 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Stock popup — MO card labels</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>formulation-edit-stock-info</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>15.170 (41.000 Kg) — Kg and units TRANSPOSED. NEW S109</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>3 STOCK ON HAND</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>unfiled</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2702,12 +2723,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -2748,12 +2769,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>S108</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>19 sites already follow the rule</t>
+          <t>As the survey recorded it</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -2761,284 +2782,452 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>The returnSum bug. Live on both clients</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>#20</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="F3" s="11" t="n">
+          <t>Corrected</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Rows 21, 26 and 27 were ALREADY green</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>#21 #26 #27</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Step 2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Nine one-line repoints, one build</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>#21 #22 #23 #24 #25 #26 #27 #28 #29</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="F4" s="11" t="n">
+          <t>S109 a</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Four repoints, one build. Commit 281e8bd8</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>#22 #23 #24 #28</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Step 3</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>The dispatch write path</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>#30</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" s="11" t="n">
+          <t>+ row 48</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>New site found while verifying</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Step 4</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Four procedure changes</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>#31 #32 #33 #34</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" s="11" t="n">
+          <t>S109 b</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>The dispatch write. Commit f4c98e91</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>#30</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Step 5</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The requirement calculation</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>#35 #36</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="11" t="n">
+          <t>S109 c</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>The view, misc release. BOTH BOXES</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Step 6</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The schema — P82 CLOSES HERE</t>
+          <t>Four procedure changes. NEEDS A MULTI-RECEIPT FIXTURE FIRST</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>#37 #38 #39 #40 #41</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="11" t="n">
+          <t>#31 #32 #33 #34</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Step 7</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The return path</t>
+          <t>The requirement calculation. Own session, own gate</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>#42 #43</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
+          <t>#35 #36</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Step 5</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The schema — P82 CLOSES HERE</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>#37 #38 #39 #40 #41</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>The return path — SURVEY FIRST, not a fix list</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>#20 #42 #43</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Row 46</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>The seven-copy helper, its own sitting</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>#25</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Row 48</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>The transposed labels</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F13" s="10" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WHERE WE ARE</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>28 green, 16 red, 4 to review, out of 48. S109 moved six rows: four repoints, the dispatch write, and the view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>NEXT TARGET — Step 3, four rows.</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>BUILD THE FIXTURE FIRST. 474 MO-0003 has ONE receipt, so per-receipt and MO-total coincide and a fix cannot be told from the bug. A second MO with TWO receipts is the precondition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>The four to review are not defects.</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>#44 a mislabelled field, #45 probably correct by design, #46 needs each caller read, #47 dead code.</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>MO-0004 on company 474 is the test.</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Do not release it. It is the before picture.</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Do not release it. It is the before picture for Step 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Pouch 4347.000 Ea is the control.</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>It must NOT move at any step. If it does, the fix is wrong.</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>#1 stock-info.ts:188 is the model.</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Read the stored count, multiply for the Kg. Do not invent a third shape.</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a living document.</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Anything found later gets a row. It does not have to be complete to be useful.</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr"/>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>S109 — the survey was wrong in BOTH directions.</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Three rows were marked red and were already green. #25 was listed as a one-line repoint and is not — it calls a helper that divides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>S109 — #23 is green but unproven.</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Deployed to both boxes and never seen on a screen; /MLO-Management redirects under the test user's roles. Same line and procedure as #22 and #24, both proven. First item at the next open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>S109 — #29 traded correct-derived for incomplete-stored.</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>On rows written BEFORE JR15 (S103) no unit count was ever stored, so those cells now read 0 or low. MEASURED: no client row is affected — Glutenull has no MR rows, Hagensborg's 24 are all Material with no mlc_id. Only sandbox 464 moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S109 — #30 is preventive on prod, not corrective.</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Neither client has ever created a dispatch order. All nine DOs on prod are sandbox, all on round ratios where the old division landed exactly. Nothing to heal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>The step numbers moved at the S108 close.</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>The return path became Step 6 and goes LAST. This sheet uses the current numbering, matching PLAN.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UNITS-BIBLE.xlsx
+++ b/UNITS-BIBLE.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Updated at the close of S111, 9 August 2026.   BOARD: 34 GREEN · 0 PART · 10 RED · 4 REVIEW, of 48.</t>
+          <t>Updated at the close of S112, 10 August 2026.   BOARD: 36 GREEN · 0 PART · 12 RED · 3 REVIEW, of 51.</t>
         </is>
       </c>
     </row>
@@ -1632,24 +1632,24 @@
       <c r="A50" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>??</t>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>XX</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Material traceability</t>
+          <t>Material traceability - A MIXED SCREEN</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>material-traceability-details:169,170</t>
+          <t>material-traceability-details.ts:169,170 + html :107 :108 :123 :124 :215 :216</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Materials are Kg-anchored BY DESIGN, so this may be correct. VERIFY AGAINST THE RULE.</t>
+          <t>RE-SCOPED S112 AND NO LONGER A REVIEW ITEM. IT IS THE ONLY WRONG NUMBER IN THE QUEUE - MO-0010 reads 10 Kg (1#) where the truth is 100 Kg, 10 units, and the Completed figure on the SAME ROW reads 100 Kg (10#) and is correct. CAUSE: mlomanagement.qty holds UNITS since the S41 flip; this screen prints it with a Kg label AND divides it by wgt_kgs_per_unit. Its neighbour received_qty really is Kg, so half the row kept working and nobody noticed. Traced end to end 10 Aug, seven hops, to Trace_MaterialDetails_SP - WHICH IS IN NO BIBLE ROW, see row 51. The procedure is INNOCENT; the defect is entirely frontend. The MATERIAL rows at :107/:108 are FINE - that alarm was withdrawn. -&gt; S113.</t>
         </is>
       </c>
     </row>
@@ -1749,74 +1749,124 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>NEW — FOUND S111, IN NO PRIOR ROW. Read the Kg inventory column one block below a corrected figure. Fixed in the same session: reads inventory_units. The matList line beside it reads the SAME property and is CORRECT — materials are Kg-anchored by rule. NEEDS MINTY'S RULING on whether it stands as a row.</t>
+          <t>ADDED S111, ACCEPTED AS ITS OWN ROW BY MINTY IN S112. Read the Kg inventory column one block below a corrected figure. Fixed in the same session: reads inventory_units. The matList line beside it reads the SAME property and is CORRECT — materials are Kg-anchored by rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Trace_MaterialDetails_SP - IN NO PRIOR ROW</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>api/models/Traceability.js:360</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>FOUND S112 by tracing row 45's defect to its source. It feeds the WHOLE Material Traceability screen and the survey never mapped it - rows 37-41 name five procedures and this is a SIXTH. It is INNOCENT: it hands over mlomanagement.qty (units) and mlomanagement.received_qty (Kg) honestly and does no arithmetic. It is listed RED only because it must gain mlomanagement.received_units for row 45's fix. -&gt; S113, and it is the fourth unmapped site found in S112.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Release screen - the PRODUCT block</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>release-mat-details html :115 :125 :157 :158 + ts :296</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>ADDED S112, AND ADDED BECAUSE S111 BROKE IT. S111 made final_qty a UNIT count for the MO detail screens; this screen reads the same property and pairs it with KILOGRAM inputs, so the auto-fill put 4.846 units into a Kg box and the guard TURNED GREEN on a release of nearly THREE TIMES the requirement. Zero client exposure - neither client has intermediates. FIXED ADDITIVELY: the backend now serves final_qty_kg alongside final_qty and this screen reads the Kg one, so rows 34 and 36 stand. Green as a consistent Kg-anchored screen, and it stays green when S113 makes it units-anchored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>reads a stored count, follows the rule</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>calculates instead</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>to review, not a defect</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>row 49 — found S111, needs Minty's ruling on whether it stands as a row</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>rows 49, 50 and 51 — added S111 and S112</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>A ROW IS GREEN WHEN IT SATISFIES PART 1, NOT WHEN IT WAS TOUCHED. A MOVING NUMBER IS NOT PROOF OF A CLOSED ROW.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>AN ADDRESS IS A CLAIM. S111 corrected SIX of them (rows 19, 34, 35, 36 and two frontend sites). READ THE LINE BEFORE PATCHING IT.</t>
         </is>
@@ -1833,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1855,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>44 IS THE CEILING, NOT 48. Rows 44, 45, 46 and 47 are REVIEW items — they close as DECISIONS, not fixes. If row 49 is accepted, the ceiling becomes 45 of 49.</t>
+          <t>47 IS THE CEILING, OF 51. Rows 44, 46 and 47 close as DECISIONS. Row 45 is NO LONGER one of them - it is the only WRONG NUMBER in the queue and it is S113.</t>
         </is>
       </c>
     </row>
@@ -2005,121 +2055,129 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>S111</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>rows 32, 33, 34, 36 — the intermediate basis</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="5" t="n">
         <v>48</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>S111 close</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>row 49 accepted as its own row</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>49</v>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>rows 50 and 51 added; row 45 rescoped to RED. NO ROW MOVED TO OK.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Rows</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Takes green to</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>STEP 5</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>the schema — qty_allocated_units. P82's ARITHMETIC CLOSES HERE</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>37,38,39,40,41</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>STEP 6</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>the return path. SURVEY FIRST — P168's cause has never been read</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>20,42,43</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ROW 25</t>
+          <t>S113</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>the seven-copy helper, its own sitting</t>
+          <t>rows 45 and 51 - THE ONLY WRONG NUMBER IN THE QUEUE. Half a session</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45,51</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
@@ -2128,21 +2186,21 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>ROW 48</t>
+          <t>S114</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>the transposed labels</t>
+          <t>THE UNITS CAPTURE on the release screen. MOVES NO ROW - it UNBLOCKS FIVE</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
@@ -2151,30 +2209,106 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>S115</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>rows 44/45/46/47 — decisions, not fixes</t>
+          <t>rows 37-41. P82's ARITHMETIC CLOSES. TRAPS 10 RETIRES</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>44,45,46,47</t>
+          <t>37,38,39,40,41</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>S116</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>rows 20/42/43, the return path. Minty's ruling S112: LAST</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>20,42,43</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>S111's PRECONDITION WAS ALREADY MEASURED AND HELD: subrecipeformulation.ship_qty is populated on EVERY row of BOTH boxes — dev 15, prod 10, zero null or zero. NO HEAL WAS NEEDED.</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>S117</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>row 25 and row 48, the tail. THE CEILING</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>25,48</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>rows 44/46/47 — decisions, not fixes</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>44,46,47</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>S114 CANNOT RUN BEFORE S113. The qty_allocated_units column exists on DEV and IS EMPTY. A read repointed against an unpopulated column shows 0 - worse than the division it replaces, because a plausible wrong number becomes an obviously wrong zero on a client-facing traceability screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>MINTY'S RULING, S112: ANY INTERMEDIATE-PRODUCT FIGURE, ANYWHERE INCLUDING TRACEABILITY, SHOWS UNITS WITH Kg DERIVED BESIDE IT - units# (Kg uom). Units are the anchor end to end. This is why rows 37-41 get REPOINTED rather than excused as correct-by-design.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2681,17 +2815,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>NO ROW MOVED TO OK. Two rows added, both already green, so the balance is unchanged at 14. Row 49 ACCEPTED. Row 50 ADDED - the release screen's product block, BROKEN BY S111 and repaired in S112. TWO RULINGS BY MINTY: units are the anchor end to end including traceability, which decides Step 5; and materials are Kg only, which re-scoped row 45 from a review item to a job. PART 1 UNTOUCHED BY CLAUDE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>S111</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>9 Aug 2026</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>ROWS 32, 33, 34 AND 36 -&gt; OK. The PART status RETIRES — no row wears it. Both intermediate procedures now serve ship_qty and inventory_units. SIX ADDRESSES CORRECTED (rows 19, 34, 35, 36 and two frontend sites). ROW 49 ADDED — a Batch Materials stock site in no prior row, found and fixed the same session; NEEDS MINTY'S RULING on whether it stands. PART 1 UNTOUCHED.</t>
         </is>
